--- a/Results_experiment/exp_2/reg_summary_11.xlsx
+++ b/Results_experiment/exp_2/reg_summary_11.xlsx
@@ -447,13 +447,13 @@
         <v>534</v>
       </c>
       <c r="D2">
-        <v>0.2027477186820075</v>
+        <v>0.2357302962805168</v>
       </c>
       <c r="E2">
-        <v>8.31031099303617</v>
+        <v>8.136595257984228</v>
       </c>
       <c r="F2">
-        <v>5.768745380073563</v>
+        <v>5.720668369436755</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -467,13 +467,13 @@
         <v>521</v>
       </c>
       <c r="D3">
-        <v>-0.1197187618555806</v>
+        <v>0.5152339535370893</v>
       </c>
       <c r="E3">
-        <v>7.509733098903823</v>
+        <v>4.941241968092238</v>
       </c>
       <c r="F3">
-        <v>4.730647616174194</v>
+        <v>3.211663648328832</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -487,13 +487,13 @@
         <v>429</v>
       </c>
       <c r="D4">
-        <v>-0.02765369933009265</v>
+        <v>0.5224640212026974</v>
       </c>
       <c r="E4">
-        <v>10.42731735350915</v>
+        <v>7.108078991769427</v>
       </c>
       <c r="F4">
-        <v>7.300495135791096</v>
+        <v>4.985810526357942</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -507,13 +507,13 @@
         <v>374</v>
       </c>
       <c r="D5">
-        <v>0.07422787169259459</v>
+        <v>0.5949046743062125</v>
       </c>
       <c r="E5">
-        <v>5.775272228937164</v>
+        <v>3.820313697239578</v>
       </c>
       <c r="F5">
-        <v>3.870118056588313</v>
+        <v>2.88745392962573</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -527,13 +527,13 @@
         <v>251</v>
       </c>
       <c r="D6">
-        <v>0.08244820708588874</v>
+        <v>0.490128938499808</v>
       </c>
       <c r="E6">
-        <v>6.195887611090168</v>
+        <v>4.61868580039212</v>
       </c>
       <c r="F6">
-        <v>4.305414533413264</v>
+        <v>3.224744938046809</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -547,13 +547,13 @@
         <v>237</v>
       </c>
       <c r="D7">
-        <v>-0.1248975033336912</v>
+        <v>-0.09621917007934266</v>
       </c>
       <c r="E7">
-        <v>6.7764293898921</v>
+        <v>6.689491976464667</v>
       </c>
       <c r="F7">
-        <v>5.298888677063119</v>
+        <v>5.587485089552302</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -567,13 +567,13 @@
         <v>223</v>
       </c>
       <c r="D8">
-        <v>0.1594329923468971</v>
+        <v>0.550242213824791</v>
       </c>
       <c r="E8">
-        <v>5.104247804421537</v>
+        <v>3.733661366225016</v>
       </c>
       <c r="F8">
-        <v>3.398767985136252</v>
+        <v>2.900367469898521</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -587,13 +587,13 @@
         <v>84</v>
       </c>
       <c r="D9">
-        <v>-0.08855365675726579</v>
+        <v>0.3903917346998468</v>
       </c>
       <c r="E9">
-        <v>15.59318671868028</v>
+        <v>11.66904681389349</v>
       </c>
       <c r="F9">
-        <v>11.52180306613445</v>
+        <v>6.769607985214818</v>
       </c>
     </row>
   </sheetData>
